--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="512">
   <si>
     <t>Filename</t>
   </si>
@@ -808,736 +808,748 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9837,0.0037,0.0027,0.0008</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9393,0.0054,0.0074,0.0112</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9586,0.0004,0.0001,0.0328</t>
+  </si>
+  <si>
+    <t>0.4474,0.0000,0.0017,0.7234</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0017,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7774,0.0031,0.1928,0.0022</t>
+  </si>
+  <si>
+    <t>0.1198,0.0005,0.9082,0.0004</t>
+  </si>
+  <si>
+    <t>0.1609,0.0001,0.9236,0.0000</t>
+  </si>
+  <si>
+    <t>0.0233,0.0015,0.9678,0.0010</t>
+  </si>
+  <si>
+    <t>0.9595,0.0018,0.0187,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9979,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.9921,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9974,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.1172,0.0011,0.6654,0.0424</t>
+  </si>
+  <si>
+    <t>0.9068,0.0004,0.1190,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.0000,0.9972,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.9970,0.0005</t>
+  </si>
+  <si>
+    <t>0.0047,0.0000,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0467,0.0001,0.9527,0.0008</t>
+  </si>
+  <si>
+    <t>0.0217,0.0000,0.9881,0.0002</t>
+  </si>
+  <si>
+    <t>0.3692,0.6366,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.9094,0.0373,0.0258,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9992,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.9955,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0070,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.2958,0.0051,0.6885,0.0017</t>
+  </si>
+  <si>
+    <t>0.2312,0.7919,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.9292,0.4936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0260,0.2373,0.6309,0.0021</t>
+  </si>
+  <si>
+    <t>0.1106,0.0034,0.8451,0.0048</t>
+  </si>
+  <si>
+    <t>0.1768,0.0013,0.8148,0.0017</t>
+  </si>
+  <si>
+    <t>0.0091,0.0001,0.9812,0.0014</t>
+  </si>
+  <si>
+    <t>0.0313,0.0003,0.9750,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0073,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9981,0.0589</t>
+  </si>
+  <si>
+    <t>0.0014,0.9045,0.0002,0.8756</t>
+  </si>
+  <si>
+    <t>0.0047,0.9769,0.0001,0.0055</t>
+  </si>
+  <si>
+    <t>0.0038,0.9888,0.0086,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9997,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0028,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.0005,0.9892,0.0071</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9992,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0031,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9854,0.0028,0.0073,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0026,0.9992,0.0009</t>
+  </si>
+  <si>
+    <t>0.9981,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8853,0.1728,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0019,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.7382,0.9874,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0031,0.9998,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.0085,0.9905,0.0027</t>
+  </si>
+  <si>
+    <t>0.0000,0.9921,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9981,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9693,0.0005,0.0326,0.0002</t>
+  </si>
+  <si>
+    <t>0.9102,0.0083,0.0409,0.0022</t>
+  </si>
+  <si>
+    <t>0.0002,0.0031,0.9993,0.0033</t>
+  </si>
+  <si>
+    <t>0.0000,0.9866,0.9827,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9534,0.9754,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.7286,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9783,0.9888,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0012,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0011,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0009,0.9998</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.7249,0.0018,0.0004,0.2646</t>
-  </si>
-  <si>
-    <t>0.1561,0.0000,0.0005,0.9517</t>
-  </si>
-  <si>
-    <t>0.9978,0.0022,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0000,0.0000</t>
+    <t>0.0001,0.9636,0.9829,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.7707,0.9777,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.7112,0.9540,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.8691,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.4624,0.9317,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9059,0.1611,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9889,0.0064,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0038,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9912,0.0089,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0016,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9908,0.0047,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0024,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
+    <t>0.9982,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.5868,0.0070,0.3496,0.0018</t>
-  </si>
-  <si>
-    <t>0.1771,0.0016,0.8694,0.0003</t>
-  </si>
-  <si>
-    <t>0.8643,0.0004,0.2130,0.0002</t>
-  </si>
-  <si>
-    <t>0.0064,0.0002,0.9929,0.0002</t>
-  </si>
-  <si>
-    <t>0.9826,0.0005,0.0075,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9974,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0509,0.9527,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9981,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8765,0.0004,0.1186,0.0013</t>
-  </si>
-  <si>
-    <t>0.0356,0.0007,0.9577,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9996,0.0012</t>
-  </si>
-  <si>
-    <t>0.0116,0.0009,0.9766,0.0021</t>
-  </si>
-  <si>
-    <t>0.0139,0.0002,0.9895,0.0002</t>
-  </si>
-  <si>
-    <t>0.0137,0.0001,0.9832,0.0016</t>
-  </si>
-  <si>
-    <t>0.0172,0.0000,0.9877,0.0004</t>
-  </si>
-  <si>
-    <t>0.6799,0.3128,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9663,0.0078,0.0099,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9996,0.0036</t>
-  </si>
-  <si>
-    <t>0.0030,0.9890,0.0119,0.0000</t>
-  </si>
-  <si>
-    <t>0.9572,0.0220,0.0018,0.0026</t>
-  </si>
-  <si>
-    <t>0.9914,0.0010,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.7191,0.3222,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9945,0.0530,0.0000</t>
-  </si>
-  <si>
-    <t>0.0328,0.6197,0.2011,0.0013</t>
-  </si>
-  <si>
-    <t>0.0116,0.0015,0.9733,0.0029</t>
-  </si>
-  <si>
-    <t>0.0324,0.0005,0.9559,0.0017</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9966,0.0012</t>
-  </si>
-  <si>
-    <t>0.0374,0.0031,0.9715,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9937,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9982,0.0307</t>
-  </si>
-  <si>
-    <t>0.0149,0.3641,0.0010,0.9455</t>
-  </si>
-  <si>
-    <t>0.0018,0.9937,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.0036,0.9926,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.9921,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0067,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9948,0.0090</t>
-  </si>
-  <si>
-    <t>0.0051,0.0000,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9993,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0012,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9934,0.0030,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.0042,0.9970,0.0007</t>
-  </si>
-  <si>
-    <t>0.9981,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0140,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0013,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9313,0.9254,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9993,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9879,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.9965,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0985,0.0008,0.9442,0.0002</t>
-  </si>
-  <si>
-    <t>0.0138,0.0022,0.9802,0.0011</t>
-  </si>
-  <si>
-    <t>0.0024,0.0032,0.9962,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.9659,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.8917,0.9454,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9706,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9675,0.8610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0022,0.9995</t>
+    <t>0.9988,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9493,0.0755,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.9362,0.0014,0.0278,0.0035</t>
+  </si>
+  <si>
+    <t>0.0098,0.0002,0.9899,0.0014</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9983,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0083,0.9869,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0085,0.9865,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.9987,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8477,0.1554,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.8980,0.0007,0.0884,0.0016</t>
+  </si>
+  <si>
+    <t>0.0641,0.0002,0.9289,0.0014</t>
+  </si>
+  <si>
+    <t>0.9422,0.0007,0.0138,0.0071</t>
+  </si>
+  <si>
+    <t>0.3349,0.0031,0.6509,0.0034</t>
+  </si>
+  <si>
+    <t>0.0010,0.0152,0.0063,0.9948</t>
+  </si>
+  <si>
+    <t>0.0006,0.9987,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9985,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9875,0.6340,0.0002</t>
+  </si>
+  <si>
+    <t>0.0231,0.9728,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.8450,0.2116,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9147,0.0854,0.0078,0.0005</t>
+  </si>
+  <si>
+    <t>0.9908,0.0065,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0000,0.0000,0.0042</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0016,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.4601,0.9765,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.4477,0.9862,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0040,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0001,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.6166,0.0008,0.4073,0.0014</t>
+  </si>
+  <si>
+    <t>0.2116,0.0001,0.8458,0.0003</t>
+  </si>
+  <si>
+    <t>0.9268,0.0011,0.0595,0.0014</t>
+  </si>
+  <si>
+    <t>0.0179,0.0002,0.0000,0.9961</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0015,0.9997</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9787,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9627,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9589,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9895,0.9932,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9027,0.9889,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9355,0.8747,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9894,0.0121,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9868,0.0123,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0064,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9363,0.9255,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0289,0.9658,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.7532,0.3499,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9705,0.0004,0.0006,0.0171</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0049,0.9940,0.0070</t>
+  </si>
+  <si>
+    <t>0.9953,0.0000,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9591,0.0352,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9142,0.0436,0.0146,0.0009</t>
+  </si>
+  <si>
+    <t>0.9005,0.0195,0.0199,0.0020</t>
+  </si>
+  <si>
+    <t>0.7131,0.0171,0.2342,0.0008</t>
+  </si>
+  <si>
+    <t>0.9760,0.0086,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9914,0.0102,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0001,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.9582,0.0011,0.0130,0.0032</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.9972,0.0005</t>
-  </si>
-  <si>
-    <t>0.0037,0.9944,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9989,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9947,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0285,0.9675,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9987,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6392,0.4234,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0005,0.0399,0.0006</t>
-  </si>
-  <si>
-    <t>0.8837,0.0001,0.1650,0.0003</t>
-  </si>
-  <si>
-    <t>0.8807,0.0029,0.0777,0.0031</t>
-  </si>
-  <si>
-    <t>0.4140,0.0063,0.4040,0.0106</t>
-  </si>
-  <si>
-    <t>0.0124,0.1088,0.0303,0.9244</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9986,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9899,0.5374,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9990,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4161,0.6875,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.8868,0.0964,0.0109,0.0021</t>
-  </si>
-  <si>
-    <t>0.9960,0.0027,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0029,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0174,0.9947,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.8453,0.9794,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.0089,0.0010,0.9893,0.0001</t>
-  </si>
-  <si>
-    <t>0.9903,0.0004,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.8456,0.0009,0.1086,0.0046</t>
-  </si>
-  <si>
-    <t>0.6479,0.0000,0.4576,0.0002</t>
-  </si>
-  <si>
-    <t>0.9714,0.0004,0.0156,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0011,0.9129,0.8013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0055,0.9920,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8002,0.2674,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2855,0.0002,0.0079,0.7404</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0024,0.9989,0.0017</t>
-  </si>
-  <si>
-    <t>0.9981,0.0000,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.7603,0.2392,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0002,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9845,0.0050,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.7100,0.0131,0.1210,0.0039</t>
-  </si>
-  <si>
-    <t>0.9257,0.0062,0.0460,0.0005</t>
-  </si>
-  <si>
-    <t>0.9885,0.0018,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0032,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9664,0.0262,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.7327,0.3920,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9433,0.0372,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0914,0.0008,0.9302,0.0010</t>
-  </si>
-  <si>
-    <t>0.9896,0.0089,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9887,0.0131,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9831,0.0095,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0038,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.0015,0.9879,0.0019</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.2725,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0189,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.7130,0.0024,0.2908,0.0012</t>
-  </si>
-  <si>
-    <t>0.0197,0.0026,0.9673,0.0019</t>
-  </si>
-  <si>
-    <t>0.0553,0.0042,0.9405,0.0005</t>
-  </si>
-  <si>
-    <t>0.2158,0.0014,0.8335,0.0002</t>
-  </si>
-  <si>
-    <t>0.1408,0.0105,0.8168,0.0012</t>
-  </si>
-  <si>
-    <t>0.9551,0.0004,0.0611,0.0001</t>
-  </si>
-  <si>
-    <t>0.9627,0.0006,0.0099,0.0040</t>
-  </si>
-  <si>
-    <t>0.3137,0.0018,0.7465,0.0006</t>
-  </si>
-  <si>
-    <t>0.0349,0.9675,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9973,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9801,0.0213,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.7962,0.2503,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0049,0.9931,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9739,0.0017,0.0077,0.0002</t>
-  </si>
-  <si>
-    <t>0.9799,0.0001,0.0172,0.0002</t>
-  </si>
-  <si>
-    <t>0.8696,0.0013,0.0081,0.0412</t>
-  </si>
-  <si>
-    <t>0.8112,0.0020,0.1146,0.0200</t>
-  </si>
-  <si>
-    <t>0.4585,0.0004,0.6107,0.0009</t>
-  </si>
-  <si>
-    <t>0.0167,0.0031,0.9794,0.0020</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.9938,0.0012</t>
-  </si>
-  <si>
-    <t>0.0142,0.0031,0.9734,0.0009</t>
-  </si>
-  <si>
-    <t>0.0070,0.0004,0.9909,0.0005</t>
-  </si>
-  <si>
-    <t>0.0039,0.3059,0.8426,0.0007</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0035,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9841,0.0119,0.0004,0.0006</t>
+    <t>0.9893,0.0071,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8704,0.1226,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.8240,0.2686,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9799,0.0104,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.4207,0.0018,0.5204,0.0022</t>
+  </si>
+  <si>
+    <t>0.9855,0.0185,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9901,0.0011,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9859,0.0159,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9892,0.0060,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.9930,0.0049,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0007,0.9957,0.0029</t>
+  </si>
+  <si>
+    <t>0.0031,0.0004,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0816,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0019,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0254,0.0021,0.9593,0.0012</t>
+  </si>
+  <si>
+    <t>0.0078,0.0005,0.9867,0.0015</t>
+  </si>
+  <si>
+    <t>0.0064,0.0374,0.9776,0.0011</t>
+  </si>
+  <si>
+    <t>0.0576,0.0038,0.9272,0.0005</t>
+  </si>
+  <si>
+    <t>0.1183,0.0181,0.8163,0.0012</t>
+  </si>
+  <si>
+    <t>0.9593,0.0003,0.0533,0.0001</t>
+  </si>
+  <si>
+    <t>0.9242,0.0036,0.0253,0.0053</t>
+  </si>
+  <si>
+    <t>0.3536,0.0015,0.6416,0.0019</t>
+  </si>
+  <si>
+    <t>0.0920,0.9252,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0084,0.9924,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9308,0.1034,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.4175,0.6708,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.2395,0.7841,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9560,0.0036,0.0171,0.0003</t>
+  </si>
+  <si>
+    <t>0.9435,0.0001,0.0644,0.0004</t>
+  </si>
+  <si>
+    <t>0.9715,0.0008,0.0044,0.0021</t>
+  </si>
+  <si>
+    <t>0.8470,0.0052,0.1167,0.0055</t>
+  </si>
+  <si>
+    <t>0.6116,0.0003,0.4073,0.0020</t>
+  </si>
+  <si>
+    <t>0.0988,0.0003,0.9214,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0007,0.9959,0.0039</t>
+  </si>
+  <si>
+    <t>0.0133,0.0009,0.9795,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.9976,0.0005</t>
+  </si>
+  <si>
+    <t>0.0065,0.0134,0.9689,0.0010</t>
+  </si>
+  <si>
+    <t>0.9966,0.0022,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0033,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0016,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9915,0.0077,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0039,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0010,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9992,0.0013</t>
+  </si>
+  <si>
+    <t>0.1104,0.0733,0.7117,0.0019</t>
+  </si>
+  <si>
+    <t>0.9226,0.0012,0.0484,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0723,0.9549,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0459,0.0005,0.9504,0.0022</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0012,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.0072,0.9910,0.0014</t>
+  </si>
+  <si>
+    <t>0.9285,0.0014,0.0603,0.0011</t>
+  </si>
+  <si>
+    <t>0.5717,0.0002,0.4456,0.0020</t>
+  </si>
+  <si>
+    <t>0.9886,0.0001,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.9867,0.0143,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9881,0.0116,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9909,0.0115,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9950,0.0048,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9952,0.0030,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9991,0.0005,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9980,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9545,0.0403,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9988,0.0020</t>
-  </si>
-  <si>
-    <t>0.3179,0.1230,0.2772,0.0031</t>
-  </si>
-  <si>
-    <t>0.9715,0.0010,0.0112,0.0020</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0055,0.0689,0.9350,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.0007,0.9911,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0060,0.9918,0.0032</t>
-  </si>
-  <si>
-    <t>0.9585,0.0004,0.0272,0.0010</t>
-  </si>
-  <si>
-    <t>0.9668,0.0001,0.0365,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0001,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0045,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9893,0.0125,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9924,0.0062,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0024,0.9919,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0036,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0164,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0490,0.0028,0.9360,0.0012</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9808,0.0509</t>
-  </si>
-  <si>
-    <t>0.0312,0.0036,0.9558,0.0012</t>
-  </si>
-  <si>
-    <t>0.0093,0.0028,0.9736,0.0075</t>
-  </si>
-  <si>
-    <t>0.9734,0.0001,0.0009,0.0192</t>
-  </si>
-  <si>
-    <t>0.0036,0.0031,0.0000,0.9984</t>
-  </si>
-  <si>
-    <t>0.0053,0.0000,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.9917,0.0001,0.0027,0.0003</t>
+    <t>0.0035,0.0006,0.9908,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.0010,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0025,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0142,0.0478,0.9132,0.0034</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0062,0.0003,0.7973,0.1854</t>
+  </si>
+  <si>
+    <t>0.1431,0.0037,0.7918,0.0067</t>
+  </si>
+  <si>
+    <t>0.0027,0.0008,0.9884,0.0137</t>
+  </si>
+  <si>
+    <t>0.9641,0.0010,0.0016,0.0162</t>
+  </si>
+  <si>
+    <t>0.0010,0.0021,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0145,0.0001,0.0001,0.9966</t>
+  </si>
+  <si>
+    <t>0.9844,0.0010,0.0010,0.0017</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1935,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1937,7 +1949,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1951,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1965,7 +1977,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1979,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1993,7 +2005,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2007,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2021,7 +2033,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2035,7 +2047,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2049,7 +2061,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2063,7 +2075,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2077,7 +2089,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2116,7 +2128,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2228,7 +2240,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2242,7 +2254,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2326,7 +2338,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2396,7 +2408,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2410,7 +2422,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2438,7 +2450,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2536,7 +2548,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2872,7 +2884,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2886,7 +2898,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -3124,7 +3136,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3295,7 +3307,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3309,7 +3321,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3323,7 +3335,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3337,7 +3349,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3351,7 +3363,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>275</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3365,7 +3377,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3379,7 +3391,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3393,7 +3405,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3407,7 +3419,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3421,7 +3433,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3435,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3449,7 +3461,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3463,7 +3475,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3477,7 +3489,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3491,7 +3503,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3505,7 +3517,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3519,7 +3531,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3530,10 +3542,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3547,7 +3559,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3558,10 +3570,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3575,7 +3587,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3589,7 +3601,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3603,7 +3615,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3617,7 +3629,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3631,7 +3643,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3645,7 +3657,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3656,10 +3668,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3673,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3687,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3701,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3715,7 +3727,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3729,7 +3741,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3743,7 +3755,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3757,7 +3769,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3771,7 +3783,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3785,7 +3797,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3799,7 +3811,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3810,10 +3822,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3827,7 +3839,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3841,7 +3853,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3855,7 +3867,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3869,7 +3881,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3880,10 +3892,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3897,7 +3909,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3911,7 +3923,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3925,7 +3937,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>340</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3939,7 +3951,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3953,7 +3965,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3967,7 +3979,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3981,7 +3993,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3995,7 +4007,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4009,7 +4021,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4023,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4037,7 +4049,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4048,10 +4060,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4065,7 +4077,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4079,7 +4091,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4093,7 +4105,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4107,7 +4119,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4121,7 +4133,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4135,7 +4147,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4149,7 +4161,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4163,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4177,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4191,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4205,7 +4217,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4219,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>352</v>
+        <v>428</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4233,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4247,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4261,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4275,7 +4287,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4289,7 +4301,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>361</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4303,7 +4315,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4317,7 +4329,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4331,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4345,7 +4357,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4359,7 +4371,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4373,7 +4385,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4387,7 +4399,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4401,7 +4413,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4415,7 +4427,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4429,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4443,7 +4455,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4457,7 +4469,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4471,7 +4483,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4485,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4499,7 +4511,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4513,7 +4525,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4527,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4541,7 +4553,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4552,10 +4564,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4569,7 +4581,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4583,7 +4595,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4597,7 +4609,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4611,7 +4623,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4625,7 +4637,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4639,7 +4651,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4653,7 +4665,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4667,7 +4679,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4681,7 +4693,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4695,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4706,10 +4718,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4723,7 +4735,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4737,7 +4749,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4751,7 +4763,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4765,7 +4777,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4779,7 +4791,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4790,10 +4802,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4807,7 +4819,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4821,7 +4833,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4835,7 +4847,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4849,7 +4861,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4863,7 +4875,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4877,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>467</v>
+        <v>361</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4891,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4905,7 +4917,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4919,7 +4931,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4933,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4947,7 +4959,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4961,7 +4973,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4975,7 +4987,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>474</v>
+        <v>361</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4989,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5000,10 +5012,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5017,7 +5029,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5031,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5045,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5059,7 +5071,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5073,7 +5085,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5087,7 +5099,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5101,7 +5113,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5115,7 +5127,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5129,7 +5141,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5143,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5157,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5171,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5185,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5199,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5213,7 +5225,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5227,7 +5239,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5241,7 +5253,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>493</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5255,7 +5267,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5269,7 +5281,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5283,7 +5295,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5297,7 +5309,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5311,7 +5323,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5325,7 +5337,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5339,7 +5351,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5353,7 +5365,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>329</v>
+        <v>504</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5367,7 +5379,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5381,7 +5393,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5395,7 +5407,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5409,7 +5421,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5423,7 +5435,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5437,7 +5449,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5451,7 +5463,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5465,7 +5477,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>340</v>
+        <v>407</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5479,7 +5491,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="517">
   <si>
     <t>Filename</t>
   </si>
@@ -808,748 +808,763 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9393,0.0054,0.0074,0.0112</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9586,0.0004,0.0001,0.0328</t>
-  </si>
-  <si>
-    <t>0.4474,0.0000,0.0017,0.7234</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9737,0.0031,0.0047,0.0030</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9133,0.0006,0.0004,0.0771</t>
+  </si>
+  <si>
+    <t>0.0288,0.0000,0.0001,0.9940</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9983,0.0010,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9958,0.0017,0.0000,0.0000</t>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6589,0.0115,0.2642,0.0025</t>
+  </si>
+  <si>
+    <t>0.0228,0.0002,0.9792,0.0006</t>
+  </si>
+  <si>
+    <t>0.4088,0.0002,0.7341,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0003,0.9924,0.0003</t>
+  </si>
+  <si>
+    <t>0.9604,0.0002,0.0306,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.9960,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0127,0.9848,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.1090,0.0004,0.8675,0.0034</t>
+  </si>
+  <si>
+    <t>0.8037,0.0004,0.2490,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0079,0.0005,0.9872,0.0010</t>
+  </si>
+  <si>
+    <t>0.0384,0.0001,0.9731,0.0003</t>
+  </si>
+  <si>
+    <t>0.1309,0.0003,0.8799,0.0011</t>
+  </si>
+  <si>
+    <t>0.0040,0.0000,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.4006,0.6281,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.7503,0.0881,0.0868,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9996,0.0043</t>
+  </si>
+  <si>
+    <t>0.0481,0.6679,0.1498,0.0002</t>
+  </si>
+  <si>
+    <t>0.9811,0.0083,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.6422,0.0029,0.3480,0.0016</t>
+  </si>
+  <si>
+    <t>0.1279,0.8919,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.9821,0.0577,0.0001</t>
+  </si>
+  <si>
+    <t>0.0078,0.8738,0.2186,0.0021</t>
+  </si>
+  <si>
+    <t>0.0492,0.0040,0.9308,0.0019</t>
+  </si>
+  <si>
+    <t>0.0169,0.0005,0.9718,0.0010</t>
+  </si>
+  <si>
+    <t>0.0588,0.0005,0.9254,0.0017</t>
+  </si>
+  <si>
+    <t>0.0049,0.0025,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.9758,0.0221,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9986,0.0444</t>
+  </si>
+  <si>
+    <t>0.0299,0.0274,0.0006,0.9736</t>
+  </si>
+  <si>
+    <t>0.0078,0.9777,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.0014,0.9958,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9964,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9956,0.0020</t>
+  </si>
+  <si>
+    <t>0.0282,0.0000,0.9798,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9989,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8804,0.0416,0.0505,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0014,0.9994,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0027,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9770,0.0341,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0024,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7815,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0180,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0407,0.9972,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.8651,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9986,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9695,0.0002,0.0404,0.0002</t>
+  </si>
+  <si>
+    <t>0.5868,0.0017,0.4825,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.0103,0.9970,0.0023</t>
+  </si>
+  <si>
+    <t>0.0001,0.9591,0.9548,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.8547,0.9453,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.8403,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9821,0.9815,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0015,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0038,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9557,0.9868,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9940,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8305,0.9930,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9888,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9603,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.4420,0.9330,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0068,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9797,0.0162,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0068,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0031,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7774,0.0031,0.1928,0.0022</t>
-  </si>
-  <si>
-    <t>0.1198,0.0005,0.9082,0.0004</t>
-  </si>
-  <si>
-    <t>0.1609,0.0001,0.9236,0.0000</t>
-  </si>
-  <si>
-    <t>0.0233,0.0015,0.9678,0.0010</t>
-  </si>
-  <si>
-    <t>0.9595,0.0018,0.0187,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9979,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0061,0.9921,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.9974,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1172,0.0011,0.6654,0.0424</t>
-  </si>
-  <si>
-    <t>0.9068,0.0004,0.1190,0.0004</t>
-  </si>
-  <si>
-    <t>0.0028,0.0000,0.9972,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9970,0.0005</t>
-  </si>
-  <si>
-    <t>0.0047,0.0000,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0467,0.0001,0.9527,0.0008</t>
-  </si>
-  <si>
-    <t>0.0217,0.0000,0.9881,0.0002</t>
-  </si>
-  <si>
-    <t>0.3692,0.6366,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.9094,0.0373,0.0258,0.0019</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9992,0.0018</t>
-  </si>
-  <si>
-    <t>0.0015,0.9955,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.9872,0.0070,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.2958,0.0051,0.6885,0.0017</t>
-  </si>
-  <si>
-    <t>0.2312,0.7919,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.9292,0.4936,0.0001</t>
-  </si>
-  <si>
-    <t>0.0260,0.2373,0.6309,0.0021</t>
-  </si>
-  <si>
-    <t>0.1106,0.0034,0.8451,0.0048</t>
-  </si>
-  <si>
-    <t>0.1768,0.0013,0.8148,0.0017</t>
-  </si>
-  <si>
-    <t>0.0091,0.0001,0.9812,0.0014</t>
-  </si>
-  <si>
-    <t>0.0313,0.0003,0.9750,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9979,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9981,0.0589</t>
-  </si>
-  <si>
-    <t>0.0014,0.9045,0.0002,0.8756</t>
-  </si>
-  <si>
-    <t>0.0047,0.9769,0.0001,0.0055</t>
-  </si>
-  <si>
-    <t>0.0038,0.9888,0.0086,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9997,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0028,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0005,0.9892,0.0071</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0031,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9854,0.0028,0.0073,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0026,0.9992,0.0009</t>
-  </si>
-  <si>
-    <t>0.9981,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8853,0.1728,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0019,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.7382,0.9874,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0031,0.9998,0.0010</t>
-  </si>
-  <si>
-    <t>0.0023,0.0085,0.9905,0.0027</t>
-  </si>
-  <si>
-    <t>0.0000,0.9921,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9981,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9693,0.0005,0.0326,0.0002</t>
-  </si>
-  <si>
-    <t>0.9102,0.0083,0.0409,0.0022</t>
-  </si>
-  <si>
-    <t>0.0002,0.0031,0.9993,0.0033</t>
-  </si>
-  <si>
-    <t>0.0000,0.9866,0.9827,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9534,0.9754,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.7286,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9783,0.9888,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0012,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0011,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0009,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9636,0.9829,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9948,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.7707,0.9777,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.7112,0.9540,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.8691,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.4624,0.9317,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9059,0.1611,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9889,0.0064,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0038,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0089,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9493,0.0755,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0000,0.0000</t>
+    <t>0.9972,0.0024,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9846,0.0203,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0215,0.0022,0.9659,0.0009</t>
+  </si>
+  <si>
+    <t>0.9746,0.0004,0.0092,0.0012</t>
+  </si>
+  <si>
+    <t>0.2580,0.0001,0.8306,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9975,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9963,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0241,0.9670,0.0029,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.9982,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7042,0.3976,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.7001,0.0009,0.3063,0.0016</t>
+  </si>
+  <si>
+    <t>0.7420,0.0001,0.4187,0.0001</t>
+  </si>
+  <si>
+    <t>0.9588,0.0011,0.0160,0.0014</t>
+  </si>
+  <si>
+    <t>0.8759,0.0113,0.0648,0.0031</t>
+  </si>
+  <si>
+    <t>0.0014,0.0878,0.0022,0.9922</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9975,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9963,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9927,0.8150,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9972,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.6744,0.4209,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9417,0.0307,0.0121,0.0015</t>
+  </si>
+  <si>
+    <t>0.9929,0.0058,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9958,0.0013,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9196,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6458,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0636,0.9848,0.0001</t>
+  </si>
+  <si>
+    <t>0.0250,0.0008,0.9732,0.0002</t>
+  </si>
+  <si>
+    <t>0.9776,0.0003,0.0091,0.0011</t>
+  </si>
+  <si>
+    <t>0.8346,0.0004,0.1960,0.0007</t>
+  </si>
+  <si>
+    <t>0.2289,0.0000,0.8643,0.0001</t>
+  </si>
+  <si>
+    <t>0.9555,0.0006,0.0303,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9585,0.8856,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.9884,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.6397,0.4847,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0450,0.0001,0.0025,0.9776</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0122,0.9947,0.0143</t>
+  </si>
+  <si>
+    <t>0.9981,0.0000,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.1467,0.7914,0.0200,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9803,0.0051,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.8853,0.0087,0.0489,0.0021</t>
+  </si>
+  <si>
+    <t>0.9187,0.0060,0.0604,0.0003</t>
+  </si>
+  <si>
+    <t>0.9896,0.0037,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0015,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.0001,0.9998,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.9362,0.0014,0.0278,0.0035</t>
-  </si>
-  <si>
-    <t>0.0098,0.0002,0.9899,0.0014</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9983,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0083,0.9869,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.9865,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8477,0.1554,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.8980,0.0007,0.0884,0.0016</t>
-  </si>
-  <si>
-    <t>0.0641,0.0002,0.9289,0.0014</t>
-  </si>
-  <si>
-    <t>0.9422,0.0007,0.0138,0.0071</t>
-  </si>
-  <si>
-    <t>0.3349,0.0031,0.6509,0.0034</t>
-  </si>
-  <si>
-    <t>0.0010,0.0152,0.0063,0.9948</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9985,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9988,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9875,0.6340,0.0002</t>
-  </si>
-  <si>
-    <t>0.0231,0.9728,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.8450,0.2116,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9147,0.0854,0.0078,0.0005</t>
-  </si>
-  <si>
-    <t>0.9908,0.0065,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0000,0.0000,0.0042</t>
-  </si>
-  <si>
-    <t>0.9982,0.0005,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9967,0.0016,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.4601,0.9765,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.4477,0.9862,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0015,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0040,0.9941,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0001,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.6166,0.0008,0.4073,0.0014</t>
-  </si>
-  <si>
-    <t>0.2116,0.0001,0.8458,0.0003</t>
-  </si>
-  <si>
-    <t>0.9268,0.0011,0.0595,0.0014</t>
-  </si>
-  <si>
-    <t>0.0179,0.0002,0.0000,0.9961</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
+    <t>0.9987,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9777,0.0126,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.1811,0.8647,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9632,0.0331,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0040,0.9950,0.0009</t>
+  </si>
+  <si>
+    <t>0.9217,0.1084,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0016,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9617,0.0090,0.0146,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0013,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.9882,0.0037,0.0038,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0088,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.5614,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.2103,0.0074,0.7457,0.0022</t>
+  </si>
+  <si>
+    <t>0.0310,0.0008,0.9680,0.0007</t>
+  </si>
+  <si>
+    <t>0.0948,0.0079,0.8823,0.0017</t>
+  </si>
+  <si>
+    <t>0.4720,0.0075,0.5265,0.0007</t>
+  </si>
+  <si>
+    <t>0.5073,0.0216,0.3765,0.0014</t>
+  </si>
+  <si>
+    <t>0.8927,0.0004,0.1852,0.0001</t>
+  </si>
+  <si>
+    <t>0.9062,0.0020,0.0443,0.0070</t>
+  </si>
+  <si>
+    <t>0.5140,0.0005,0.5361,0.0010</t>
+  </si>
+  <si>
+    <t>0.0218,0.9768,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9988,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9678,0.0321,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.3349,0.8015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5586,0.5551,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9680,0.0017,0.0086,0.0006</t>
+  </si>
+  <si>
+    <t>0.9331,0.0002,0.0762,0.0005</t>
+  </si>
+  <si>
+    <t>0.9378,0.0017,0.0086,0.0074</t>
+  </si>
+  <si>
+    <t>0.3971,0.0348,0.4812,0.0173</t>
+  </si>
+  <si>
+    <t>0.8830,0.0003,0.1330,0.0009</t>
+  </si>
+  <si>
+    <t>0.0056,0.0011,0.9903,0.0052</t>
+  </si>
+  <si>
+    <t>0.0029,0.0017,0.9891,0.0024</t>
+  </si>
+  <si>
+    <t>0.0534,0.0168,0.9137,0.0015</t>
+  </si>
+  <si>
+    <t>0.0103,0.0002,0.9884,0.0003</t>
+  </si>
+  <si>
+    <t>0.0060,0.0286,0.9533,0.0015</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0026,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9895,0.0113,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0028,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9990,0.0009</t>
+  </si>
+  <si>
+    <t>0.2369,0.0921,0.5121,0.0015</t>
+  </si>
+  <si>
+    <t>0.8991,0.0014,0.0425,0.0077</t>
+  </si>
+  <si>
+    <t>0.0034,0.0001,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.0131,0.9839,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0303,0.0005,0.9683,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0084,0.0039,0.9767,0.0036</t>
+  </si>
+  <si>
+    <t>0.0018,0.0085,0.9917,0.0072</t>
+  </si>
+  <si>
+    <t>0.4521,0.0023,0.4263,0.0086</t>
+  </si>
+  <si>
+    <t>0.8590,0.0002,0.1420,0.0013</t>
+  </si>
+  <si>
+    <t>0.9713,0.0017,0.0065,0.0014</t>
+  </si>
+  <si>
+    <t>0.9871,0.0077,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9899,0.0103,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0048,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0063,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0152,0.0065,0.9553,0.0040</t>
+  </si>
+  <si>
+    <t>0.0014,0.0006,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0163,0.9859,0.0004</t>
+  </si>
+  <si>
+    <t>0.0092,0.0033,0.9767,0.0028</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0002,0.7906,0.1790</t>
+  </si>
+  <si>
+    <t>0.0107,0.0012,0.9725,0.0072</t>
+  </si>
+  <si>
+    <t>0.0322,0.0003,0.9577,0.0053</t>
+  </si>
+  <si>
+    <t>0.9527,0.0002,0.0004,0.0397</t>
+  </si>
+  <si>
+    <t>0.0060,0.0013,0.0000,0.9979</t>
+  </si>
+  <si>
+    <t>0.0115,0.0000,0.0000,0.9981</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0001,1.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.9363,0.9255,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0289,0.9658,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.7532,0.3499,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0004,0.0006,0.0171</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0049,0.9940,0.0070</t>
-  </si>
-  <si>
-    <t>0.9953,0.0000,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9591,0.0352,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0001,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9142,0.0436,0.0146,0.0009</t>
-  </si>
-  <si>
-    <t>0.9005,0.0195,0.0199,0.0020</t>
-  </si>
-  <si>
-    <t>0.7131,0.0171,0.2342,0.0008</t>
-  </si>
-  <si>
-    <t>0.9760,0.0086,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9893,0.0071,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8704,0.1226,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.8240,0.2686,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9799,0.0104,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.4207,0.0018,0.5204,0.0022</t>
-  </si>
-  <si>
-    <t>0.9855,0.0185,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9901,0.0011,0.0002,0.0029</t>
-  </si>
-  <si>
-    <t>0.9859,0.0159,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9892,0.0060,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0049,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0007,0.9957,0.0029</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0816,0.9948,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0019,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0254,0.0021,0.9593,0.0012</t>
-  </si>
-  <si>
-    <t>0.0078,0.0005,0.9867,0.0015</t>
-  </si>
-  <si>
-    <t>0.0064,0.0374,0.9776,0.0011</t>
-  </si>
-  <si>
-    <t>0.0576,0.0038,0.9272,0.0005</t>
-  </si>
-  <si>
-    <t>0.1183,0.0181,0.8163,0.0012</t>
-  </si>
-  <si>
-    <t>0.9593,0.0003,0.0533,0.0001</t>
-  </si>
-  <si>
-    <t>0.9242,0.0036,0.0253,0.0053</t>
-  </si>
-  <si>
-    <t>0.3536,0.0015,0.6416,0.0019</t>
-  </si>
-  <si>
-    <t>0.0920,0.9252,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.9924,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9308,0.1034,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.4175,0.6708,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2395,0.7841,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9560,0.0036,0.0171,0.0003</t>
-  </si>
-  <si>
-    <t>0.9435,0.0001,0.0644,0.0004</t>
-  </si>
-  <si>
-    <t>0.9715,0.0008,0.0044,0.0021</t>
-  </si>
-  <si>
-    <t>0.8470,0.0052,0.1167,0.0055</t>
-  </si>
-  <si>
-    <t>0.6116,0.0003,0.4073,0.0020</t>
-  </si>
-  <si>
-    <t>0.0988,0.0003,0.9214,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.9959,0.0039</t>
-  </si>
-  <si>
-    <t>0.0133,0.0009,0.9795,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.9976,0.0005</t>
-  </si>
-  <si>
-    <t>0.0065,0.0134,0.9689,0.0010</t>
-  </si>
-  <si>
-    <t>0.9966,0.0022,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0033,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0016,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9915,0.0077,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0039,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0010,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9992,0.0013</t>
-  </si>
-  <si>
-    <t>0.1104,0.0733,0.7117,0.0019</t>
-  </si>
-  <si>
-    <t>0.9226,0.0012,0.0484,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0723,0.9549,0.0008</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0459,0.0005,0.9504,0.0022</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0028,0.0072,0.9910,0.0014</t>
-  </si>
-  <si>
-    <t>0.9285,0.0014,0.0603,0.0011</t>
-  </si>
-  <si>
-    <t>0.5717,0.0002,0.4456,0.0020</t>
-  </si>
-  <si>
-    <t>0.9886,0.0001,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.9867,0.0143,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9881,0.0116,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9909,0.0115,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9950,0.0048,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0030,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9908,0.0020</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.0142,0.0478,0.9132,0.0034</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.0062,0.0003,0.7973,0.1854</t>
-  </si>
-  <si>
-    <t>0.1431,0.0037,0.7918,0.0067</t>
-  </si>
-  <si>
-    <t>0.0027,0.0008,0.9884,0.0137</t>
-  </si>
-  <si>
-    <t>0.9641,0.0010,0.0016,0.0162</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0145,0.0001,0.0001,0.9966</t>
-  </si>
-  <si>
-    <t>0.9844,0.0010,0.0010,0.0017</t>
+    <t>0.9784,0.0002,0.0007,0.0080</t>
   </si>
 </sst>
 </file>
@@ -1935,7 +1950,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1949,7 +1964,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1963,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1977,7 +1992,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1991,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2005,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2019,7 +2034,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2033,7 +2048,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2047,7 +2062,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2061,7 +2076,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2075,7 +2090,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2089,7 +2104,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2103,7 +2118,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2117,7 +2132,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2131,7 +2146,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2145,7 +2160,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2159,7 +2174,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2173,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2187,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2201,7 +2216,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2215,7 +2230,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2229,7 +2244,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2243,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2257,7 +2272,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2271,7 +2286,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2285,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2299,7 +2314,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2313,7 +2328,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2327,7 +2342,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2341,7 +2356,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2355,7 +2370,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2369,7 +2384,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2383,7 +2398,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2397,7 +2412,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2408,10 +2423,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2425,7 +2440,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2439,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2450,10 +2465,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2467,7 +2482,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2481,7 +2496,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2495,7 +2510,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2509,7 +2524,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2523,7 +2538,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2537,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2548,10 +2563,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2565,7 +2580,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2579,7 +2594,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2593,7 +2608,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2607,7 +2622,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2621,7 +2636,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2635,7 +2650,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2649,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2663,7 +2678,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2677,7 +2692,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2691,7 +2706,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2705,7 +2720,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2719,7 +2734,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2733,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2747,7 +2762,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2761,7 +2776,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2775,7 +2790,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2789,7 +2804,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2803,7 +2818,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2817,7 +2832,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2831,7 +2846,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2845,7 +2860,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2859,7 +2874,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2873,7 +2888,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2887,7 +2902,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2901,7 +2916,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2915,7 +2930,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2929,7 +2944,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2943,7 +2958,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2957,7 +2972,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2971,7 +2986,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2985,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2999,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3013,7 +3028,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3027,7 +3042,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3041,7 +3056,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3055,7 +3070,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3069,7 +3084,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3083,7 +3098,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3097,7 +3112,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3111,7 +3126,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3125,7 +3140,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3139,7 +3154,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3153,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3167,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3181,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3195,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3209,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3223,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3237,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3251,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3265,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3279,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3542,7 +3557,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3570,7 +3585,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3808,7 +3823,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3822,7 +3837,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3951,7 +3966,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3965,7 +3980,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3979,7 +3994,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3993,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4007,7 +4022,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4021,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4035,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4049,7 +4064,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4060,10 +4075,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4077,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4091,7 +4106,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4105,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4119,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4130,10 +4145,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4147,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4161,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4175,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4189,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4203,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4217,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4231,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4245,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4259,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4273,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4287,7 +4302,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4301,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>271</v>
+        <v>432</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4340,7 +4355,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>435</v>
@@ -4508,7 +4523,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
         <v>447</v>
@@ -4620,7 +4635,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
         <v>455</v>
@@ -4662,7 +4677,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
         <v>458</v>
@@ -4732,7 +4747,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
         <v>463</v>
@@ -4788,7 +4803,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
         <v>467</v>
@@ -4889,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>361</v>
+        <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4903,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4917,7 +4932,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4931,7 +4946,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4945,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4959,7 +4974,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4973,7 +4988,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4987,7 +5002,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>361</v>
+        <v>481</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5001,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5015,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5029,7 +5044,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5043,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5057,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5071,7 +5086,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5085,7 +5100,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5099,7 +5114,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5113,7 +5128,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5127,7 +5142,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5141,7 +5156,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5152,10 +5167,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5169,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5183,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5197,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5211,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5225,7 +5240,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5239,7 +5254,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5253,7 +5268,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>271</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5267,7 +5282,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5281,7 +5296,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5295,7 +5310,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5309,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5323,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5337,7 +5352,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5351,7 +5366,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5365,7 +5380,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5379,7 +5394,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5393,7 +5408,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5407,7 +5422,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5421,7 +5436,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5435,7 +5450,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5449,7 +5464,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5463,7 +5478,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>408</v>
+        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5491,7 +5506,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
